--- a/odk_forms/rapid_assessment.xlsx
+++ b/odk_forms/rapid_assessment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/ree140_csiro_au/Documents/projects/grdc-mice/analysis/mousecast/odk_forms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ree140/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_0BFAB65EBEAFD8C7287981A043CE4285CA3CE358" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD7A899-A0C2-E449-87BD-74DC56F9D913}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCD5029-DDC7-9A4E-BC6B-059D843C29AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="860" yWindow="500" windowWidth="21880" windowHeight="27040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="860" yWindow="500" windowWidth="42800" windowHeight="27040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Determines what kinds of values are allowed and how the field is displayed. For certain types, further customization is possible using the appearance and parameters columns.
@@ -49,7 +48,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Variable name. It may not contain spaces and must start with a letter or underscore. You should use a short, descriptive name and can use underscores to separate words. For example: date_of_birth.</t>
@@ -63,7 +61,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The user-visible question text for the field. For example: "When was ${first_name} born?" This text can optionally reference other fields or be styled using subsets of Markdown and HTML.
@@ -78,7 +75,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>A hint that will be shown to the user below the question's label in smaller text.
@@ -93,7 +89,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Leave blank for questions that aren't required. Write yes for questions that are required. You can also use an expression to make a question conditionally required.
@@ -108,7 +103,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>An expression that determines whether a question will be displayed to a user or not. Lets you define branching or skip logic. 
@@ -123,7 +117,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>One or more modifiers that determine how the question will be displayed.
@@ -138,7 +131,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>An expression that determines whether a user-provided answer will be allowed or not. Constraint expressions use . to mean the value of the current field.
@@ -153,7 +145,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>A message shown when the constraint expression evaluates to false.
@@ -168,7 +159,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>An expression that will be evaluated to determine the value of the field.
@@ -185,7 +175,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Used with select questions to filter the choices shown to the user. The expression will be evaluated against each choice. If it evaluates to true, the choice is included.
@@ -201,7 +190,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>One or more pairs of keys and values that configure aspects of a question type that are not appearance-related.
@@ -216,7 +204,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>Specify the filename of an image to display in addition to or instead of a text label.
@@ -241,7 +228,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The name of a list. To group choices in a list, give them all the same list_name.
@@ -256,7 +242,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The value that will be saved when this choice is selected. This is the value you will use in analysis.
@@ -271,7 +256,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The user-visible text for the choice. This text can have translations or be styled using subsets of Markdown and HTML.</t>
@@ -285,7 +269,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>You can include any number of additional columns to provide information about each list item. These are useful to chain multiple selects together or look up data based on a selected item.
@@ -312,7 +295,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The title that will be displayed to anyone who uses this form.
@@ -327,7 +309,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The unique ID that identifies this form to tools that use it. It may not contain spaces and must start with a letter or underscore. You should use a short, descriptive name and can use underscores to separate words. 
@@ -343,7 +324,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>The unique version code that identifies the current state of the form. A common convention is to use a format like yyyymmddrr. For example, 2017021501 is the 1st revision from Feb 15th, 2017.
@@ -358,7 +338,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
-            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>An expression that will be used to represent a specific filled form created from this form definition. This will be used in lists of filled forms and on the server.
@@ -372,17 +351,359 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="291">
+  <si>
+    <t>list_name</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>crop_group</t>
+  </si>
+  <si>
+    <t>cereals</t>
+  </si>
+  <si>
+    <t>Cereals</t>
+  </si>
+  <si>
+    <t>group_cereals.png</t>
+  </si>
+  <si>
+    <t>legumes</t>
+  </si>
+  <si>
+    <t>Legumes</t>
+  </si>
+  <si>
+    <t>group_pulses.png</t>
+  </si>
+  <si>
+    <t>oilseeds</t>
+  </si>
+  <si>
+    <t>Oilseeds</t>
+  </si>
+  <si>
+    <t>group_oilseeds.png</t>
+  </si>
+  <si>
+    <t>cotton</t>
+  </si>
+  <si>
+    <t>Cotton</t>
+  </si>
+  <si>
+    <t>group_cotton.png</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>Unknown crop</t>
+  </si>
+  <si>
+    <t>group_unknown.png</t>
+  </si>
+  <si>
+    <t>pasture</t>
+  </si>
+  <si>
+    <t>Pasture</t>
+  </si>
+  <si>
+    <t>group_grass.png</t>
+  </si>
+  <si>
+    <t>bare_soil</t>
+  </si>
+  <si>
+    <t>Bare soil</t>
+  </si>
+  <si>
+    <t>group_fallow.png</t>
+  </si>
+  <si>
+    <t>crop_variety</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>Wheat</t>
+  </si>
+  <si>
+    <t>barley</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>oats</t>
+  </si>
+  <si>
+    <t>Oats</t>
+  </si>
+  <si>
+    <t>sorghum</t>
+  </si>
+  <si>
+    <t>Sorghum</t>
+  </si>
+  <si>
+    <t>maize</t>
+  </si>
+  <si>
+    <t>Maize</t>
+  </si>
+  <si>
+    <t>millet</t>
+  </si>
+  <si>
+    <t>Millet</t>
+  </si>
+  <si>
+    <t>triticale</t>
+  </si>
+  <si>
+    <t>Triticale</t>
+  </si>
+  <si>
+    <t>cereal_other</t>
+  </si>
+  <si>
+    <t>Unknown cereal</t>
+  </si>
+  <si>
+    <t>chickpea</t>
+  </si>
+  <si>
+    <t>Chickpea</t>
+  </si>
+  <si>
+    <t>faba_bean</t>
+  </si>
+  <si>
+    <t>Faba bean</t>
+  </si>
+  <si>
+    <t>field_pea</t>
+  </si>
+  <si>
+    <t>Field pea</t>
+  </si>
+  <si>
+    <t>mungbean</t>
+  </si>
+  <si>
+    <t>Mungbean</t>
+  </si>
+  <si>
+    <t>lentil</t>
+  </si>
+  <si>
+    <t>Lentil</t>
+  </si>
+  <si>
+    <t>lupin</t>
+  </si>
+  <si>
+    <t>Lupin</t>
+  </si>
+  <si>
+    <t>peanut</t>
+  </si>
+  <si>
+    <t>Peanut</t>
+  </si>
+  <si>
+    <t>soybean</t>
+  </si>
+  <si>
+    <t>Soybean</t>
+  </si>
+  <si>
+    <t>vetch</t>
+  </si>
+  <si>
+    <t>Vetch</t>
+  </si>
+  <si>
+    <t>lucerne</t>
+  </si>
+  <si>
+    <t>Lucerne</t>
+  </si>
+  <si>
+    <t>legume_other</t>
+  </si>
+  <si>
+    <t>Unknown legume</t>
+  </si>
+  <si>
+    <t>canola</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>sunflower</t>
+  </si>
+  <si>
+    <t>Sunflower</t>
+  </si>
+  <si>
+    <t>safflower</t>
+  </si>
+  <si>
+    <t>Safflower</t>
+  </si>
+  <si>
+    <t>linseed</t>
+  </si>
+  <si>
+    <t>Linseed</t>
+  </si>
+  <si>
+    <t>oilseed_other</t>
+  </si>
+  <si>
+    <t>Unknown oilseed</t>
+  </si>
+  <si>
+    <t>cotton_other</t>
+  </si>
+  <si>
+    <t>Unknown cotton</t>
+  </si>
+  <si>
+    <t>crop_stage</t>
+  </si>
+  <si>
+    <t>sown</t>
+  </si>
+  <si>
+    <t>Sown</t>
+  </si>
+  <si>
+    <t>stage_sown.png</t>
+  </si>
+  <si>
+    <t>seedling</t>
+  </si>
+  <si>
+    <t>Seedling</t>
+  </si>
+  <si>
+    <t>stage_germination.png</t>
+  </si>
+  <si>
+    <t>vegetative</t>
+  </si>
+  <si>
+    <t>Vegetative</t>
+  </si>
+  <si>
+    <t>stage_tillering.png</t>
+  </si>
+  <si>
+    <t>flowering</t>
+  </si>
+  <si>
+    <t>Flowering</t>
+  </si>
+  <si>
+    <t>stage_flowering.png</t>
+  </si>
+  <si>
+    <t>ripening</t>
+  </si>
+  <si>
+    <t>Ripening</t>
+  </si>
+  <si>
+    <t>stage_grain_fill.png</t>
+  </si>
+  <si>
+    <t>stubble</t>
+  </si>
+  <si>
+    <t>Stubble</t>
+  </si>
+  <si>
+    <t>stage_stubble.png</t>
+  </si>
+  <si>
+    <t>bait_history</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>unsure</t>
+  </si>
+  <si>
+    <t>Unsure</t>
+  </si>
+  <si>
+    <t>bait_dosage</t>
+  </si>
+  <si>
+    <t>znp25</t>
+  </si>
+  <si>
+    <t>ZnP25</t>
+  </si>
+  <si>
+    <t>znp50</t>
+  </si>
+  <si>
+    <t>ZnP50</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>yes_no</t>
+  </si>
+  <si>
+    <t>irrigation_type</t>
+  </si>
+  <si>
+    <t>flood</t>
+  </si>
+  <si>
+    <t>Flood irrigation</t>
+  </si>
+  <si>
+    <t>spray</t>
+  </si>
+  <si>
+    <t>Spray / sprinkler irrigation</t>
+  </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>label</t>
-  </si>
-  <si>
     <t>hint</t>
   </si>
   <si>
@@ -408,9 +729,6 @@
   </si>
   <si>
     <t>parameters</t>
-  </si>
-  <si>
-    <t>image</t>
   </si>
   <si>
     <t>repeat_count</t>
@@ -453,9 +771,6 @@
     <t>Or identifier for this survey location (optional)</t>
   </si>
   <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>farmer</t>
   </si>
   <si>
@@ -465,9 +780,6 @@
     <t>Full name of farmer (or property owner / manager)</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
     <t>regex(., '.*\s+.*')</t>
   </si>
   <si>
@@ -489,9 +801,6 @@
     <t>select_one crop_group</t>
   </si>
   <si>
-    <t>crop_group</t>
-  </si>
-  <si>
     <t>What's in the paddock currently?</t>
   </si>
   <si>
@@ -501,30 +810,30 @@
     <t>select_one crop_variety</t>
   </si>
   <si>
-    <t>crop_variety</t>
-  </si>
-  <si>
     <t>Crop type</t>
   </si>
   <si>
     <t xml:space="preserve">(or closest, if not shown) </t>
   </si>
   <si>
+    <t>(${crop_group} = 'cereals' or ${crop_group} = 'legumes' or ${crop_group} = 'oilseeds')</t>
+  </si>
+  <si>
     <t>group = ${crop_group}</t>
   </si>
   <si>
     <t>select_one crop_stage</t>
   </si>
   <si>
-    <t>crop_stage</t>
-  </si>
-  <si>
     <t>Growth stage</t>
   </si>
   <si>
     <t>What is the most advanced phase of the current crop?</t>
   </si>
   <si>
+    <t>${crop_group} != 'pasture' and ${crop_group} != 'bare_soil'</t>
+  </si>
+  <si>
     <t>decimal</t>
   </si>
   <si>
@@ -561,9 +870,6 @@
     <t>select_one bait_history</t>
   </si>
   <si>
-    <t>bait_history</t>
-  </si>
-  <si>
     <t>Was mouse bait spread in last 2 months?</t>
   </si>
   <si>
@@ -573,9 +879,6 @@
     <t>select_one bait_dosage</t>
   </si>
   <si>
-    <t>bait_dosage</t>
-  </si>
-  <si>
     <t>Bait dosage</t>
   </si>
   <si>
@@ -594,9 +897,6 @@
     <t>select_one irrigation_type</t>
   </si>
   <si>
-    <t>irrigation_type</t>
-  </si>
-  <si>
     <t>Irrigation type</t>
   </si>
   <si>
@@ -609,9 +909,6 @@
     <t>burrow_conducted</t>
   </si>
   <si>
-    <t>Were active burrow searches conducted?</t>
-  </si>
-  <si>
     <t>integer</t>
   </si>
   <si>
@@ -648,9 +945,6 @@
     <t>Why were active burrow transects not conducted?</t>
   </si>
   <si>
-    <t>Please briefly explain why transects were not completed at this site</t>
-  </si>
-  <si>
     <t>${burrow_conducted} = 'no'</t>
   </si>
   <si>
@@ -708,13 +1002,25 @@
     <t>Were chew cards deployed and assessed?</t>
   </si>
   <si>
+    <t>mice_chewed_cards</t>
+  </si>
+  <si>
+    <t>Were any of the cards chewed by mice?</t>
+  </si>
+  <si>
+    <t>If answered yes, you need to enter the results for every card below (both with and without mice chews), be sure to log them in the correct order.</t>
+  </si>
+  <si>
+    <t>${chew_conducted} = 'yes'</t>
+  </si>
+  <si>
     <t>chew_cards_deployed</t>
   </si>
   <si>
-    <t>How many cards were successfully deployed in total?</t>
-  </si>
-  <si>
-    <t>${chew_conducted} = 'yes'</t>
+    <t>How many cards were successfully assessed in total?</t>
+  </si>
+  <si>
+    <t>Do not count tampered cards (e.g., damaged or removed by a fox).</t>
   </si>
   <si>
     <t>chew_low_warning</t>
@@ -723,7 +1029,7 @@
     <t>⚠️ **You have deployed fewer cards than expected for a survey, please check!**</t>
   </si>
   <si>
-    <t>${chew_conducted} = 'yes' and ${chew_cards_deployed} &gt; 0 and ${chew_cards_deployed} &lt; 10</t>
+    <t>${chew_conducted} = 'yes' and ${mice_chewed_cards} = 'yes' and ${chew_cards_deployed} &gt; 0 and ${chew_cards_deployed} &lt; 10</t>
   </si>
   <si>
     <t>chew_not_conducted_reason</t>
@@ -744,6 +1050,9 @@
     <t>Chew card ${chew_position}</t>
   </si>
   <si>
+    <t>${chew_conducted} = 'yes' and ${mice_chewed_cards} = 'yes'</t>
+  </si>
+  <si>
     <t>${chew_cards_deployed}</t>
   </si>
   <si>
@@ -780,7 +1089,7 @@
     <t>Chew card count</t>
   </si>
   <si>
-    <t>if(${chew_conducted} = 'yes', count(${chew_cards}), 0)</t>
+    <t>if(${chew_conducted} = 'yes' and ${mice_chewed_cards} = 'yes', count(${chew_cards}), if(${chew_conducted} = 'yes' and ${mice_chewed_cards} = 'no', ${chew_cards_deployed}, 0))</t>
   </si>
   <si>
     <t>start</t>
@@ -831,7 +1140,7 @@
     <t>Mean card chewed (%)</t>
   </si>
   <si>
-    <t>if(${chew_conducted} = 'yes' and ${chew_card_count} &gt; 0, round(sum(${chew_percent}) div ${chew_card_count}, 1), 0)</t>
+    <t>if(${chew_conducted} = 'yes' and ${mice_chewed_cards} = 'yes' and ${chew_card_count} &gt; 0, round(sum(${chew_percent}) div ${chew_card_count}, 1), 0)</t>
   </si>
   <si>
     <t>cards_with_chew</t>
@@ -840,7 +1149,7 @@
     <t>Cards with mouse chew</t>
   </si>
   <si>
-    <t>if(${chew_conducted} = 'yes', count(${chew_percent}[. &gt; 0]), 0)</t>
+    <t>if(${chew_conducted} = 'yes' and ${mice_chewed_cards} = 'yes', count(${chew_percent}[. &gt; 0]), 0)</t>
   </si>
   <si>
     <t>transects_with_burrow</t>
@@ -889,273 +1198,6 @@
 Surveyor: ${surveyor}&lt;br&gt;Farmer: ${farmer}&lt;br&gt;Site: ${site_name}&lt;br&gt;Date: ${date_today}&lt;br&gt;&lt;br&gt;Crop group: ${crop_group}&lt;br&gt;Crop type: ${crop_variety}&lt;br&gt;Growth stage: ${crop_stage}&lt;br&gt;Recently mouse baited: ${bait_history}&lt;br&gt;Irrigated: ${irrigated}&lt;br&gt;Ground cover: ${ground_cover}%&lt;br&gt;&lt;br&gt;Active burrow transects: ${burrow_conducted}&lt;br&gt;Transects completed: ${total_transects}&lt;br&gt;Total length surveyed: ${total_transect_m} m&lt;br&gt;Total active burrows: ${total_burrows}&lt;br&gt;Transects with at least one burrow: ${transects_with_burrow}&lt;br&gt;&lt;br&gt;Chew cards deployed: ${chew_conducted}&lt;br&gt;Cards assessed: ${chew_card_count}&lt;br&gt;Cards with mouse chew: ${cards_with_chew}&lt;br&gt;Mean card chewed: ${avg_chew}%</t>
   </si>
   <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>cereals</t>
-  </si>
-  <si>
-    <t>Cereals</t>
-  </si>
-  <si>
-    <t>group_cereals.png</t>
-  </si>
-  <si>
-    <t>group_pulses.png</t>
-  </si>
-  <si>
-    <t>oilseeds</t>
-  </si>
-  <si>
-    <t>Oilseeds</t>
-  </si>
-  <si>
-    <t>group_oilseeds.png</t>
-  </si>
-  <si>
-    <t>cotton</t>
-  </si>
-  <si>
-    <t>Cotton</t>
-  </si>
-  <si>
-    <t>group_cotton.png</t>
-  </si>
-  <si>
-    <t>group_grass.png</t>
-  </si>
-  <si>
-    <t>Bare soil</t>
-  </si>
-  <si>
-    <t>group_fallow.png</t>
-  </si>
-  <si>
-    <t>wheat</t>
-  </si>
-  <si>
-    <t>Wheat</t>
-  </si>
-  <si>
-    <t>barley</t>
-  </si>
-  <si>
-    <t>Barley</t>
-  </si>
-  <si>
-    <t>oats</t>
-  </si>
-  <si>
-    <t>Oats</t>
-  </si>
-  <si>
-    <t>sorghum</t>
-  </si>
-  <si>
-    <t>Sorghum</t>
-  </si>
-  <si>
-    <t>maize</t>
-  </si>
-  <si>
-    <t>Maize</t>
-  </si>
-  <si>
-    <t>millet</t>
-  </si>
-  <si>
-    <t>Millet</t>
-  </si>
-  <si>
-    <t>triticale</t>
-  </si>
-  <si>
-    <t>Triticale</t>
-  </si>
-  <si>
-    <t>cereal_other</t>
-  </si>
-  <si>
-    <t>Unknown cereal</t>
-  </si>
-  <si>
-    <t>chickpea</t>
-  </si>
-  <si>
-    <t>Chickpea</t>
-  </si>
-  <si>
-    <t>faba_bean</t>
-  </si>
-  <si>
-    <t>Faba bean</t>
-  </si>
-  <si>
-    <t>field_pea</t>
-  </si>
-  <si>
-    <t>Field pea</t>
-  </si>
-  <si>
-    <t>mungbean</t>
-  </si>
-  <si>
-    <t>Mungbean</t>
-  </si>
-  <si>
-    <t>lentil</t>
-  </si>
-  <si>
-    <t>Lentil</t>
-  </si>
-  <si>
-    <t>lupin</t>
-  </si>
-  <si>
-    <t>Lupin</t>
-  </si>
-  <si>
-    <t>soybean</t>
-  </si>
-  <si>
-    <t>Soybean</t>
-  </si>
-  <si>
-    <t>canola</t>
-  </si>
-  <si>
-    <t>Canola</t>
-  </si>
-  <si>
-    <t>sunflower</t>
-  </si>
-  <si>
-    <t>Sunflower</t>
-  </si>
-  <si>
-    <t>safflower</t>
-  </si>
-  <si>
-    <t>Safflower</t>
-  </si>
-  <si>
-    <t>linseed</t>
-  </si>
-  <si>
-    <t>Linseed</t>
-  </si>
-  <si>
-    <t>peanut</t>
-  </si>
-  <si>
-    <t>Peanut</t>
-  </si>
-  <si>
-    <t>oilseed_other</t>
-  </si>
-  <si>
-    <t>Unknown oilseed</t>
-  </si>
-  <si>
-    <t>cotton_other</t>
-  </si>
-  <si>
-    <t>Unknown cotton</t>
-  </si>
-  <si>
-    <t>stubble</t>
-  </si>
-  <si>
-    <t>Stubble</t>
-  </si>
-  <si>
-    <t>stage_stubble.png</t>
-  </si>
-  <si>
-    <t>sown</t>
-  </si>
-  <si>
-    <t>Sown</t>
-  </si>
-  <si>
-    <t>stage_sown.png</t>
-  </si>
-  <si>
-    <t>Seedling</t>
-  </si>
-  <si>
-    <t>stage_germination.png</t>
-  </si>
-  <si>
-    <t>Vegetative</t>
-  </si>
-  <si>
-    <t>stage_tillering.png</t>
-  </si>
-  <si>
-    <t>flowering</t>
-  </si>
-  <si>
-    <t>Flowering</t>
-  </si>
-  <si>
-    <t>stage_flowering.png</t>
-  </si>
-  <si>
-    <t>Ripening</t>
-  </si>
-  <si>
-    <t>stage_grain_fill.png</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>unsure</t>
-  </si>
-  <si>
-    <t>Unsure</t>
-  </si>
-  <si>
-    <t>znp25</t>
-  </si>
-  <si>
-    <t>ZnP25</t>
-  </si>
-  <si>
-    <t>znp50</t>
-  </si>
-  <si>
-    <t>ZnP50</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>yes_no</t>
-  </si>
-  <si>
-    <t>flood</t>
-  </si>
-  <si>
-    <t>Flood irrigation</t>
-  </si>
-  <si>
-    <t>spray</t>
-  </si>
-  <si>
-    <t>Spray / sprinkler irrigation</t>
-  </si>
-  <si>
     <t>form_title</t>
   </si>
   <si>
@@ -1177,61 +1219,16 @@
     <t>20260511011852</t>
   </si>
   <si>
-    <t>Legumes</t>
-  </si>
-  <si>
-    <t>legumes</t>
-  </si>
-  <si>
-    <t>pasture</t>
-  </si>
-  <si>
-    <t>Pasture</t>
-  </si>
-  <si>
-    <t>bare_soil</t>
-  </si>
-  <si>
-    <t>Unknown legume</t>
-  </si>
-  <si>
-    <t>legume_other</t>
-  </si>
-  <si>
-    <t>vetch</t>
-  </si>
-  <si>
-    <t>lucerne</t>
-  </si>
-  <si>
-    <t>Vetch</t>
-  </si>
-  <si>
-    <t>Lucerne</t>
-  </si>
-  <si>
-    <t>(${crop_group} = 'cereals' or ${crop_group} = 'legumes' or ${crop_group} = 'oilseeds')</t>
-  </si>
-  <si>
-    <t>Unknown crop</t>
-  </si>
-  <si>
-    <t>group_unknown.png</t>
-  </si>
-  <si>
-    <t>${crop_group} != 'pasture' and ${crop_group} != 'bare_soil'</t>
-  </si>
-  <si>
-    <t>This generates a data entry box for every card below. Do not count tampered cards (e.g., damaged or removed by a fox).</t>
-  </si>
-  <si>
-    <t>seedling</t>
-  </si>
-  <si>
-    <t>vegetative</t>
-  </si>
-  <si>
-    <t>ripening</t>
+    <t>Briefly explain why burrow searches were not completed at this site</t>
+  </si>
+  <si>
+    <t>Were burrow searches conducted?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you properly searched for burrows yesterday but found none, still answer "yes". </t>
+  </si>
+  <si>
+    <t xml:space="preserve">i.e., set-up for flood or spray irrigation (you don't need to know if it had been recently irrigated or not). </t>
   </si>
 </sst>
 </file>
@@ -2003,7 +2000,7 @@
     <tabColor rgb="FF009ECC"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N524"/>
+  <dimension ref="A1:N525"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -2020,7 +2017,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -2029,122 +2026,122 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>128</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>20</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>141</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="112" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -2157,125 +2154,125 @@
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="70" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>42</v>
+        <v>151</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F8" t="s">
-        <v>277</v>
+        <v>153</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>156</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>280</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="28" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>161</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>53</v>
+        <v>163</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="M10" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="56" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>58</v>
+        <v>168</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="L11" t="s">
-        <v>59</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="84" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>62</v>
+        <v>171</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>63</v>
+        <v>172</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
@@ -2288,413 +2285,417 @@
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="98" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>177</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>70</v>
+        <v>178</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>290</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="11"/>
+        <v>183</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>289</v>
+      </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>90</v>
+        <v>195</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>287</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F19" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>199</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="G20" t="s">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="N20" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
       <c r="J21" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>205</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="J24" t="s">
-        <v>107</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>214</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>281</v>
+        <v>216</v>
+      </c>
+      <c r="D26" t="s">
+        <v>217</v>
       </c>
       <c r="E26" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s">
-        <v>112</v>
-      </c>
-      <c r="H26" t="s">
-        <v>83</v>
-      </c>
-      <c r="I26" t="s">
-        <v>84</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
-      </c>
-      <c r="C27" t="s">
-        <v>114</v>
+        <v>219</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="E27" t="s">
+        <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>115</v>
+        <v>218</v>
+      </c>
+      <c r="H27" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" t="s">
-        <v>29</v>
+        <v>223</v>
       </c>
       <c r="F28" t="s">
-        <v>119</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>92</v>
+        <v>134</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>226</v>
+      </c>
+      <c r="D29" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" t="s">
+        <v>98</v>
       </c>
       <c r="F29" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" t="s">
-        <v>95</v>
-      </c>
-      <c r="N29" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
-      </c>
-      <c r="J30" t="s">
-        <v>99</v>
+        <v>230</v>
+      </c>
+      <c r="F30" t="s">
+        <v>231</v>
+      </c>
+      <c r="G30" t="s">
+        <v>200</v>
+      </c>
+      <c r="N30" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>78</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>233</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
-      </c>
-      <c r="E31" t="s">
-        <v>29</v>
-      </c>
-      <c r="H31" t="s">
-        <v>53</v>
-      </c>
-      <c r="I31" t="s">
-        <v>126</v>
+        <v>233</v>
+      </c>
+      <c r="J31" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G32" t="s">
-        <v>130</v>
-      </c>
-      <c r="L32" t="s">
-        <v>131</v>
+        <v>98</v>
+      </c>
+      <c r="H32" t="s">
+        <v>163</v>
+      </c>
+      <c r="I32" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>120</v>
+        <v>237</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>238</v>
+      </c>
+      <c r="E33" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33" t="s">
+        <v>239</v>
+      </c>
+      <c r="G33" t="s">
+        <v>240</v>
+      </c>
+      <c r="L33" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" t="s">
-        <v>133</v>
-      </c>
-      <c r="J34" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
+      <c r="A35" t="s">
+        <v>202</v>
+      </c>
+      <c r="B35" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" t="s">
+        <v>243</v>
+      </c>
+      <c r="J35" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="36" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>138</v>
+        <v>246</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>137</v>
+        <v>245</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2708,15 +2709,17 @@
       <c r="M36" s="3"/>
     </row>
     <row r="37" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="11" t="s">
-        <v>139</v>
+      <c r="A37" s="3" t="s">
+        <v>247</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>140</v>
+        <v>248</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>139</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
@@ -2727,182 +2730,186 @@
       <c r="M37" s="3"/>
     </row>
     <row r="38" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" t="s">
-        <v>142</v>
-      </c>
-      <c r="J38" t="s">
-        <v>143</v>
-      </c>
+      <c r="A38" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
     </row>
     <row r="39" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="C39" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="J39" t="s">
-        <v>107</v>
+        <v>253</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>254</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>255</v>
       </c>
       <c r="J40" t="s">
-        <v>148</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="J41" t="s">
-        <v>151</v>
+        <v>258</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>152</v>
+        <v>259</v>
       </c>
       <c r="C42" t="s">
-        <v>153</v>
+        <v>260</v>
       </c>
       <c r="J42" t="s">
-        <v>154</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s">
-        <v>155</v>
+        <v>262</v>
       </c>
       <c r="C43" t="s">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="J43" t="s">
-        <v>157</v>
+        <v>264</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="B44" t="s">
-        <v>158</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="E44" t="s">
-        <v>29</v>
-      </c>
-      <c r="H44" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" t="s">
-        <v>31</v>
+        <v>265</v>
+      </c>
+      <c r="C44" t="s">
+        <v>266</v>
+      </c>
+      <c r="J44" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>21</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>161</v>
+        <v>134</v>
+      </c>
+      <c r="B45" t="s">
+        <v>268</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="E45" t="s">
-        <v>29</v>
+        <v>98</v>
+      </c>
+      <c r="H45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="E46" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="47" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" t="s">
-        <v>167</v>
-      </c>
-      <c r="C47" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" t="s">
-        <v>169</v>
-      </c>
+      <c r="A47" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
     </row>
     <row r="48" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="4"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" t="s">
+        <v>278</v>
+      </c>
+      <c r="D48" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="49" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="3"/>
       <c r="B49" s="4"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
@@ -9966,7 +9973,7 @@
       <c r="L519" s="3"/>
       <c r="M519" s="3"/>
     </row>
-    <row r="520" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+    <row r="520" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A520" s="3"/>
       <c r="B520" s="4"/>
       <c r="C520" s="3"/>
@@ -9981,7 +9988,7 @@
       <c r="L520" s="3"/>
       <c r="M520" s="3"/>
     </row>
-    <row r="521" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+    <row r="521" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A521" s="3"/>
       <c r="B521" s="4"/>
       <c r="C521" s="3"/>
@@ -9996,7 +10003,7 @@
       <c r="L521" s="3"/>
       <c r="M521" s="3"/>
     </row>
-    <row r="522" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+    <row r="522" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A522" s="3"/>
       <c r="B522" s="4"/>
       <c r="C522" s="3"/>
@@ -10011,7 +10018,7 @@
       <c r="L522" s="3"/>
       <c r="M522" s="3"/>
     </row>
-    <row r="523" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+    <row r="523" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A523" s="3"/>
       <c r="B523" s="4"/>
       <c r="C523" s="3"/>
@@ -10026,7 +10033,7 @@
       <c r="L523" s="3"/>
       <c r="M523" s="3"/>
     </row>
-    <row r="524" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+    <row r="524" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A524" s="3"/>
       <c r="B524" s="4"/>
       <c r="C524" s="3"/>
@@ -10040,6 +10047,21 @@
       <c r="K524" s="3"/>
       <c r="L524" s="3"/>
       <c r="M524" s="3"/>
+    </row>
+    <row r="525" spans="1:13" ht="14" x14ac:dyDescent="0.15">
+      <c r="A525" s="3"/>
+      <c r="B525" s="4"/>
+      <c r="C525" s="3"/>
+      <c r="D525" s="3"/>
+      <c r="E525" s="3"/>
+      <c r="F525" s="3"/>
+      <c r="G525" s="3"/>
+      <c r="H525" s="3"/>
+      <c r="I525" s="3"/>
+      <c r="J525" s="3"/>
+      <c r="K525" s="3"/>
+      <c r="L525" s="3"/>
+      <c r="M525" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
@@ -10142,7 +10164,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="13" t="s">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>1</v>
@@ -10151,652 +10173,652 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>171</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>266</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>175</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>178</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>279</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>269</v>
+        <v>22</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>182</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>270</v>
+        <v>24</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>185</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>186</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>188</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>190</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>191</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>36</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>194</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>195</v>
+        <v>38</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>196</v>
+        <v>39</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" t="s">
-        <v>198</v>
-      </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>45</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>204</v>
+        <v>47</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>206</v>
+        <v>49</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>51</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>209</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>211</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>55</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>223</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>224</v>
+        <v>57</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>213</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>214</v>
+        <v>59</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>275</v>
+        <v>61</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>274</v>
+        <v>62</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>276</v>
+        <v>63</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>272</v>
+        <v>64</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>271</v>
+        <v>65</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>267</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>215</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>216</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>217</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>219</v>
+        <v>70</v>
       </c>
       <c r="C30" t="s">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="C31" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>225</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="D33" t="s">
-        <v>179</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>229</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>231</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>233</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>234</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c r="E36" t="s">
-        <v>236</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>283</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="E37" t="s">
-        <v>238</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>239</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>240</v>
+        <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>284</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>242</v>
+        <v>95</v>
       </c>
       <c r="E39" t="s">
-        <v>243</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
-        <v>244</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>245</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>246</v>
+        <v>102</v>
       </c>
       <c r="C42" t="s">
-        <v>247</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>249</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>250</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>253</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>245</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>255</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>256</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B49" t="s">
-        <v>257</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>258</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -10814,38 +10836,38 @@
     <row r="62" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="63" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="64" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="97" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="98" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="99" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -13646,7 +13668,7 @@
       <c r="D575" s="10"/>
     </row>
     <row r="576" spans="1:4" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <conditionalFormatting sqref="A1">
     <cfRule type="expression" dxfId="9" priority="20">
@@ -13664,12 +13686,12 @@
       <formula>LEN(TRIM(A23))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:D27 A5:D5 B6:C6 F7:X17 E18:X32 D18:D34 F33:X34 E34:E39 F35:F39 H35:X39 D36:D39 A40:X499 B35:D35">
+  <conditionalFormatting sqref="A7:D27 B34:D34 A5:D5 B6:C6 F7:X17 E18:X32 D18:D33 F33:X34 E34:E39 D35:D39 F35:F39 H35:X39 A40:X499">
     <cfRule type="expression" dxfId="5" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:D8 A7:A27 E18:H32 B22:D27 D28:D34 F33:H34 E34:E39 F35:F39 H35:H39 D36:D39 A40:H499 B35:D35">
+  <conditionalFormatting sqref="B7:D8 A7:A27 E18:H32 B22:D27 D28:D33 F33:H34 B34:D34 E34:E39 D35:D39 F35:F39 H35:H39 A40:H499">
     <cfRule type="notContainsBlanks" dxfId="4" priority="7">
       <formula>LEN(TRIM(A7))&gt;0</formula>
     </cfRule>
@@ -13719,27 +13741,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="D2" s="12"/>
     </row>
